--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>MFG</t>
   </si>
@@ -656,123 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27670400</v>
+      </c>
+      <c r="E8" s="3">
         <v>26036000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20641300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20906700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23106600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22199900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22413300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23063100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25570500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9627600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10816200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10415100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12862100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12867300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12991300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,39 +824,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>27670400</v>
+      </c>
+      <c r="E10" s="3">
         <v>26036000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20641300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20906700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23106600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22199900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22413300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23063100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25570500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -866,9 +875,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,39 +998,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-350100</v>
+      </c>
+      <c r="E14" s="3">
         <v>11600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-103500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>31100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>505100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1107000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>141800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4475100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-178900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1030,47 +1049,50 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1517500</v>
+      </c>
+      <c r="E15" s="3">
         <v>1375100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1178100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1255800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1364000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1509700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1456600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1554700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1674300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17817800</v>
+      </c>
+      <c r="E17" s="3">
         <v>18077200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14430800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15015800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17628700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17410300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16521400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17538900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18217300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4203400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3702500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2367200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2489000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4997300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3552000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9852600</v>
+      </c>
+      <c r="E18" s="3">
         <v>7958800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6210500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5890900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5477900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4789600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5891900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5524200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7353200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5424200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7113800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8047800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10373100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7870000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9439300</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1244,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1241,75 +1274,81 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2359400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1513800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1024200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3806900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>132000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3447300</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11370200</v>
+      </c>
+      <c r="E21" s="3">
         <v>9333900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7388600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7146700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6841900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6299400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7348400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7079000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9027500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4155300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9846700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8120800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8025500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9424400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7491800</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10202700</v>
+      </c>
+      <c r="E23" s="3">
         <v>7947200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6314100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5859800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4972800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5896600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5750000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1049200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7532200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3064800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8627500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7023600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6566100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8002000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5992000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2315200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2012800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1796500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1646200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>499800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1580400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1500900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-22600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1804300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>582100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2498600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2162400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2044000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>36400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>125500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7887500</v>
+      </c>
+      <c r="E26" s="3">
         <v>5934400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4517500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4213600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4473100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4316300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4249200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1071800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5727800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2482700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6129000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4861200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4522100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7965700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5866600</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7852800</v>
+      </c>
+      <c r="E27" s="3">
         <v>5912800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4489100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4179000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4368500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4258800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4168800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>871500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5428600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2312400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6114500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4303800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4445300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7839400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5855400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,9 +1853,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1817,75 +1886,81 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>2359400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1513800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1024200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3806900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3447300</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7852800</v>
+      </c>
+      <c r="E33" s="3">
         <v>5912800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4489100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4179000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4368500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4258800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4168800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>871500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5428600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2312400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6114500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4303800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4445300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7839400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5855400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7852800</v>
+      </c>
+      <c r="E35" s="3">
         <v>5912800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4489100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4179000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4368500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4258800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4168800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>871500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5428600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2312400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6114500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4303800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4445300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7839400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5855400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,122 +2158,129 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>387206400</v>
+      </c>
+      <c r="E41" s="3">
         <v>484033800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>470502200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>495175700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>412868700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>433837400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>381682000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>407080600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>449370200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>303605000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>264247000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>206292000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15339800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11466700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10998300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>395090100</v>
+      </c>
+      <c r="E42" s="3">
         <v>350102600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>294345400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>235325700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>232627900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>243407800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>316661200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>249249800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>215983600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>260240000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>322177000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>228831000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>549634000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>550699000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>464937000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
         <v>11920800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9978000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10071300</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2198,8 +2290,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2216,9 +2308,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2246,8 +2341,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2264,39 +2359,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>87968400</v>
+      </c>
+      <c r="E45" s="3">
         <v>80549500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>97290400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>99385100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>112276200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>78549500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>75379100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72698500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72170500</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2312,39 +2410,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>874181100</v>
+      </c>
+      <c r="E46" s="3">
         <v>918906400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>877917600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>843735600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>773383000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>761060300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>777549800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>732204500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>740701300</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,153 +2461,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>294301200</v>
+      </c>
+      <c r="E47" s="3">
         <v>255362300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>280455600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>309927300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>396239700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>424102100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>349394100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>294228400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>347410900</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>2070100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2410200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2725300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3815500</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7152900</v>
+      </c>
+      <c r="E48" s="3">
         <v>7496500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7533400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8318800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9025300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10266400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10256500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9358400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10462100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13023300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13251900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7643400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12263600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9871600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9988000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5548600</v>
+      </c>
+      <c r="E49" s="3">
         <v>5401700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4794200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4308300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4951600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5607900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5912000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5597200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10288700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1207900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>488500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4662100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>637300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>638400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>686500</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>89099100</v>
+      </c>
+      <c r="E52" s="3">
         <v>75229100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>54289000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>71831300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68019800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>81397500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>74319900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>59025600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>69607500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>405300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>413500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5532500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3662300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5801700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7564000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1900821000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1891981200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1842399600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1912665000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1952222100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2039676800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1994935800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1812040700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1930495700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1278910000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1397370000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1344860000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1588320000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1615870000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1503910000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,8 +2914,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2814,15 +2944,15 @@
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>12006800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>23974500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2832,41 +2962,44 @@
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>272756600</v>
+      </c>
+      <c r="E58" s="3">
         <v>293834100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>308224900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>250625600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>277862000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>203267300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>195339500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>169471100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>186758600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2880,57 +3013,63 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>191062100</v>
+      </c>
+      <c r="E59" s="3">
         <v>161036000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>164744400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>174054400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>107440200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>133076400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>145642400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>129840000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>130358500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1804900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2005500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>424500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1963800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1773800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1902700</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2958,8 +3097,8 @@
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
+      <c r="L60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -2976,105 +3115,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>145902500</v>
+      </c>
+      <c r="E61" s="3">
         <v>129829100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>115365200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>116799800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>143045800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>179768800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>151299600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>126335500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>176455300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>92697700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>106459000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>93656100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>89079600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>79572100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>76494800</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>98260700</v>
+      </c>
+      <c r="E62" s="3">
         <v>78332600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>50150100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>63958000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>60854500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>73972000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>77097800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>57758000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>53723600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>896200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1455400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5104500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>300000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>129300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>143300</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1829100700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1821704800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1774222500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1843394000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1876452300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1955026800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1914418200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1729069500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1838021300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1226200000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1339590000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1286980000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1530660000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1564090000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1463490000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3414,23 +3581,26 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>713200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1511000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>2826400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>3411300</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>3709700</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>42962000</v>
+      </c>
+      <c r="E72" s="3">
         <v>40378400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>36619600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>38319100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>39168900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>39979200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>38792900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>35335400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>37689700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5862500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5384300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19661900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4858800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7985800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14519200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>71170900</v>
+      </c>
+      <c r="E76" s="3">
         <v>69731900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>67650900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>68705500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74752300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>83693400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>79498400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>78959600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>85372700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>52707500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57071700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>56378400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>54835000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48370900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>36706000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7852800</v>
+      </c>
+      <c r="E81" s="3">
         <v>5912800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4489100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4179000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4368500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4258800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4168800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>871500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5428600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2312400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6114500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4303800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4445300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7839400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5855400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1457800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1326300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1144900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1227400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1333200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1475900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1418800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1517900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1635100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1092300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1210800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1139000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1457800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1420800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1498100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-37687600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-38385700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1973500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17014700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>19124600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>111881700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-57596400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-49118800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30173800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7740900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1742700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>47183700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>53799800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11733800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16176500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-608100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-634000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-417300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-487800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-348300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-971000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-797800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-385400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-545900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2749200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2801600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1533600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4131100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1458700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1577600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41938200</v>
+      </c>
+      <c r="E94" s="3">
         <v>25329800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>13105100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>49691300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15321000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-88280600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-53981700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>49518600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21808700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-81674000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43101900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>18570300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3772400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-57149400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16659800</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2318800</v>
+      </c>
+      <c r="E96" s="3">
         <v>2032900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1552300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1575600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1620500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1722400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1769400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1718400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1212400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1408000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1249200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1375600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1378700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1951800</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3967400</v>
+      </c>
+      <c r="E100" s="3">
         <v>10873900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12908600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>45092100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17068900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>38698800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>72652300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>25161300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>59519600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>75729000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40078300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6405100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-53986900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>69064300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>26811200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6190300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-772700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>11265300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6225700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5107800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2056900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1884500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-294700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>96100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-75900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-202300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>266300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>287800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>287300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-12900</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-69468100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2954700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>35305500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>118023800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25980400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>64356800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40810300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25266300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7633100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1720000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1483200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>59615200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3873100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>468400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6037900</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
